--- a/data/서울특별시/노원구립도서관.xlsx
+++ b/data/서울특별시/노원구립도서관.xlsx
@@ -7,38 +7,38 @@
   </bookViews>
   <sheets>
     <sheet name="입력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="불암도서관" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="화랑도서관" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="마들이음도서관" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="공릉행복(공릉1동)도서관" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="노원문화원(공릉1동)도서관" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="도란도란(공릉1동)도서관" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="파랑새(상계2동)도서관" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="해솔(상계5동)도서관" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="나무(상계6,7동)도서관" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="메아리(상계6,7동)도서관" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="반디(상계8동)도서관" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="꿈꾸는(월계1동)도서관" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="초안산숲속(월계2동)도서관" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="한내행복발전소(월계3동)도서관" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="책누리(중계본동)도서관" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="하늘(중계2,3동)도서관" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="향기나무도서관" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="중계사랑(중계4동)도서관" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="가재울지혜마루(하계1동)도서관" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="노원중앙도서관" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="월계도서관" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="노원중앙도서관" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="불암도서관" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="화랑도서관" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="마들이음도서관" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="공릉행복(공릉1동)도서관" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="노원문화원(공릉1동)도서관" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="도란도란(공릉1동)도서관" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="책이랑친구랑(공릉2동)도서관" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="파랑새(상계2동)도서관" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="해솔(상계5동)도서관" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="나무(상계6,7동)도서관" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="메아리(상계6,7동)도서관" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="반디(상계8동)도서관" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="꿈꾸는(월계1동)도서관" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="초안산숲속(월계2동)도서관" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="한내행복발전소(월계3동)도서관" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="책누리(중계본동)도서관" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="하늘(중계2,3동)도서관" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="향기나무도서관" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="중계사랑(중계4동)도서관" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="가재울지혜마루(하계1동)도서관" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="상계도서관" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="월계어린이도서관" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="책이랑친구랑(공릉2동)도서관" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="푸른숲(상계1동)도서관" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="수락(상계3,4동)도서관" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="노원구청(상계6,7동)도서관" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="한울(상계9동)도서관" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="달내(월계2동)도서관" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="한내지혜의숲(월계3동)도서관" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="책사랑북카페(중계1동)도서관" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="열린(하계2동)도서관" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="푸른숲(상계1동)도서관" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="수락(상계3,4동)도서관" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="노원구청(상계6,7동)도서관" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="한울(상계9동)도서관" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="달내(월계2동)도서관" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="한내지혜의숲(월계3동)도서관" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="책사랑북카페(중계1동)도서관" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="열린(하계2동)도서관" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="월계도서관" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,14 +525,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -540,21 +541,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>나무작은일반자료실</t>
+          <t>상계2동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -562,7 +564,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>나무작은일반자료실</t>
+          <t>상계2동자료실</t>
         </is>
       </c>
     </row>
@@ -577,11 +579,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -617,14 +619,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -632,7 +635,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>평생교육원자료실</t>
+          <t>상계5동자료실</t>
         </is>
       </c>
     </row>
@@ -644,61 +647,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1=c.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진; 신승미 옮김</t>
+          <t>이민진; 이미정 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>평생교육원자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>평생교육원자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>평생교육원자료실</t>
+          <t>상계5동자료실</t>
         </is>
       </c>
     </row>
@@ -720,7 +680,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,14 +713,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -768,21 +729,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>상계8동자료실</t>
+          <t>나무작은일반자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -790,7 +752,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>상계8동자료실</t>
+          <t>나무작은일반자료실</t>
         </is>
       </c>
     </row>
@@ -800,6 +762,146 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>평생교육원자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>평생교육원자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>평생교육원자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.1=c.2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이민진; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>평생교육원자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -845,14 +947,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -860,21 +963,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>월계1동자료실</t>
+          <t>상계8동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -882,143 +986,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>월계1동자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>초안산숲속자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>초안산숲속자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>초안산숲속자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>초안산숲속자료실</t>
+          <t>상계8동자료실</t>
         </is>
       </c>
     </row>
@@ -1073,14 +1041,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1088,21 +1057,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>한내행복자료실</t>
+          <t>월계1동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1110,7 +1080,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>한내행복자료실</t>
+          <t>월계1동자료실</t>
         </is>
       </c>
     </row>
@@ -1120,6 +1090,146 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>초안산숲속자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>초안산숲속자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>초안산숲속자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이민진; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>초안산숲속자료실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1165,14 +1275,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1180,21 +1291,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>중계본동자료실</t>
+          <t>한내행복자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1202,143 +1314,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>중계본동자료실</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>중계2,3동자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.1=c.2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>중계2,3동자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.2=c.2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>중계2,3동자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>중계2,3동자료실</t>
+          <t>한내행복자료실</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1336,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1393,14 +1369,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1408,21 +1385,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>향기나무 일반자료실</t>
+          <t>중계본동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1430,7 +1408,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>향기나무 일반자료실</t>
+          <t>중계본동자료실</t>
         </is>
       </c>
     </row>
@@ -1445,11 +1423,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1485,14 +1463,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2=c.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1500,7 +1479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>중계4동자료실</t>
+          <t>중계2,3동자료실</t>
         </is>
       </c>
     </row>
@@ -1515,6 +1494,7 @@
           <t>일반 843-이39ㅍ-v.2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1522,7 +1502,53 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>중계4동자료실</t>
+          <t>중계2,3동자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>중계2,3동자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.1=c.2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>중계2,3동자료실</t>
         </is>
       </c>
     </row>
@@ -1537,14 +1563,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1577,14 +1603,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1592,7 +1619,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>일반자료실(불암_2층)</t>
+          <t>노원중앙종합자료실</t>
         </is>
       </c>
     </row>
@@ -1604,9 +1631,10 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>청소년 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>843-이39파-v.2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -1614,29 +1642,76 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>청소년자료실(불암_3층)</t>
+          <t>노원중앙종합자료실</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>843-이39파-v.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민진; 이미정 옮김</t>
+          <t>이민진; 신승미 옮김</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>일반자료실(불암_2층)</t>
+          <t>노원중앙종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>파친코 구슬</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>863-뒤51ㅍ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>엘리자 수아 뒤사팽; 이상해 옮김</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>노원중앙종합자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>애프터 양</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DV 688.2-코15ㅇ=c.1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>코고나다 감독</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>노원중앙디지털자료실</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1733,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1691,14 +1766,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1706,21 +1782,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>하계1동자료실</t>
+          <t>향기나무 일반자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -1728,7 +1805,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>하계1동자료실</t>
+          <t>향기나무 일반자료실</t>
         </is>
       </c>
     </row>
@@ -1743,14 +1820,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1783,110 +1860,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이39파-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진; 신승미 옮김</t>
+          <t>이민진; 이미정 옮김</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>노원중앙종합자료실</t>
+          <t>중계4동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843-이39파-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진; 신승미 옮김</t>
+          <t>이민진; 이미정 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>노원중앙종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>843-이39ㅍ-v.2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>노원중앙종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>파친코 구슬</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>863-뒤51ㅍ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>엘리자 수아 뒤사팽; 이상해 옮김</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>노원중앙종합자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>애프터 양</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DV 688.2-코15ㅇ=c.1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>코고나다 감독</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>노원중앙디지털자료실</t>
+          <t>중계4동자료실</t>
         </is>
       </c>
     </row>
@@ -1901,14 +1914,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1941,22 +1954,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>파친코: 이민진 장편소설. 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>하계1동자료실</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>843-이민진ㅍ-v.1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진; 신승미 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>생각서재(월계_3F)</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>하계1동자료실</t>
         </is>
       </c>
     </row>
@@ -2011,14 +2048,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2033,14 +2071,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2063,6 +2102,7 @@
           <t>331.3713-김16ㅍ</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>김광식</t>
@@ -2125,14 +2165,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843.6-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>843.6-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2147,14 +2188,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.6-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>843.6-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2181,10 +2223,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2217,14 +2259,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1=c.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2232,29 +2275,30 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>공릉2동자료실</t>
+          <t>푸른숲일반자료실(상호대차제공불가)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진; 이미정 옮김</t>
+          <t>이민진; 신승미 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>공릉2동자료실</t>
+          <t>푸른숲일반자료실(상호대차제공불가)</t>
         </is>
       </c>
     </row>
@@ -2309,14 +2353,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2324,21 +2369,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>푸른숲일반자료실</t>
+          <t>상계3,4동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2346,7 +2392,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>푸른숲일반자료실</t>
+          <t>상계3,4동자료실</t>
         </is>
       </c>
     </row>
@@ -2401,14 +2447,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>CM 843.6-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2416,21 +2463,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>상계3,4동자료실</t>
+          <t>노원구청자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>CM 843.6-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2438,7 +2486,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>상계3,4동자료실</t>
+          <t>노원구청자료실</t>
         </is>
       </c>
     </row>
@@ -2493,14 +2541,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CM 843.6-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2508,21 +2557,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>노원구청자료실</t>
+          <t>상계9동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CM 843.6-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2530,7 +2580,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>노원구청자료실</t>
+          <t>상계9동자료실</t>
         </is>
       </c>
     </row>
@@ -2585,14 +2635,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2600,21 +2651,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>상계9동자료실</t>
+          <t>월계2동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2622,7 +2674,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>상계9동자료실</t>
+          <t>월계2동자료실</t>
         </is>
       </c>
     </row>
@@ -2637,14 +2689,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2677,14 +2729,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -2692,29 +2745,53 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>화랑종합자료실</t>
+          <t>일반자료실(불암_2층)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>파친코: 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>이민진; 이미정 옮김</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>일반자료실(불암_2층)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>화랑종합자료실</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>청소년 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>이민진; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>청소년자료실(불암_3층)</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2813,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2769,14 +2846,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2784,21 +2862,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>월계2동자료실</t>
+          <t>한내지혜의숲자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2806,7 +2885,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>월계2동자료실</t>
+          <t>한내지혜의숲자료실</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2907,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2861,14 +2940,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2876,21 +2956,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>한내지혜의숲자료실</t>
+          <t>중계1동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2898,7 +2979,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>한내지혜의숲자료실</t>
+          <t>중계1동자료실</t>
         </is>
       </c>
     </row>
@@ -2953,14 +3034,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2968,21 +3050,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>중계1동자료실</t>
+          <t>하계2동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -2990,7 +3073,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>중계1동자료실</t>
+          <t>하계2동자료실</t>
         </is>
       </c>
     </row>
@@ -3000,6 +3083,77 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>책 이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>청구기호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>음원 여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>도서관 내 열람실</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>파친코: 이민진 장편소설. 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>843-이민진ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>이민진; 신승미 옮김</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>생각서재(월계_3F)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3045,44 +3199,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이민진; 신승미 옮김</t>
+          <t>이민진; 이미정 옮김</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>하계2동자료실</t>
+          <t>화랑종합자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진; 신승미 옮김</t>
+          <t>이민진; 이미정 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>하계2동자료실</t>
+          <t>화랑종합자료실</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3137,14 +3293,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -3164,12 +3321,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843.6-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진; 신승미 옮김</t>
+          <t>이민진; 이미정 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3181,14 +3339,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>843-이39파-v.1</t>
-        </is>
-      </c>
+          <t>843.6-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -3211,6 +3370,7 @@
           <t>843-이39파-v.2</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -3225,14 +3385,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>843.6-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>843.6-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>이민진; 신승미 옮김</t>
@@ -3247,17 +3408,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>843-이39파-v.1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>이민진; 이미정 옮김</t>
+          <t>이민진; 신승미 옮김</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3271,7 +3433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3317,14 +3479,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -3339,14 +3502,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -3355,98 +3519,6 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>일반자료실(2층)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>책 이름</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>청구기호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>음원 여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>저자</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>도서관 내 열람실</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>문화원자료실</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>파친코: 이민진 장편소설. 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>이민진; 이미정 옮김</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>문화원자료실</t>
         </is>
       </c>
     </row>
@@ -3501,14 +3573,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -3516,21 +3589,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>공릉1동자료실</t>
+          <t>문화원자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -3538,7 +3612,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>공릉1동자료실</t>
+          <t>문화원자료실</t>
         </is>
       </c>
     </row>
@@ -3593,14 +3667,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -3608,21 +3683,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>상계2동자료실</t>
+          <t>공릉1동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -3630,7 +3706,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>상계2동자료실</t>
+          <t>공릉1동자료실</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3725,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -3685,14 +3761,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 1</t>
+          <t>파친코: 이민진 장편소설. 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.1</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>이민진; 이미정 옮김</t>
@@ -3700,29 +3777,30 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>상계5동자료실</t>
+          <t>공릉2동자료실</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>파친코: 이민진 장편소설. 2</t>
+          <t>파친코: 이민진 장편소설. 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>일반 843-이39ㅍ-v.2</t>
-        </is>
-      </c>
+          <t>일반 843-이39ㅍ-v.1=c.2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이민진; 이미정 옮김</t>
+          <t>이민진; 신승미 옮김</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>상계5동자료실</t>
+          <t>공릉2동자료실</t>
         </is>
       </c>
     </row>
